--- a/servers/maze_main_server/conf.d/data/maze_kongfu_display_v8【迷宫-武力值对应表现等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_kongfu_display_v8【迷宫-武力值对应表现等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C541D304-788B-4AF3-A9B5-60D99AF3B121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B646E-7947-4975-A0D2-AC56A181969E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{5297CD8D-800C-4E54-9ACA-71C16FF2D0B0}"/>
   </bookViews>
@@ -76,11 +76,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LONG_S</t>
+    <t>LONG_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>INT_S</t>
+    <t>INT_S_C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -88,7 +88,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +98,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -124,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -480,7 +489,7 @@
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
